--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
@@ -775,7 +775,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -787,47 +787,46 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="inlineStr">
+          <t>8518</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">45
 </t>
         </is>
       </c>
+      <c r="T4" s="3" t="n"/>
       <c r="U4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -836,19 +835,25 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="n"/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="W4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -866,116 +871,139 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">317
+</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">316
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">072
+</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="W5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">262
 </t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2620
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">927
-</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="n"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">702
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="n"/>
       <c r="Y5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">68
@@ -996,131 +1024,135 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 5
-</t>
-        </is>
-      </c>
+      <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="n"/>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">072
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="n"/>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">42
+</t>
         </is>
       </c>
       <c r="Z6" s="3" t="n"/>
@@ -1137,95 +1169,100 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">305
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+1
+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="n"/>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">316
+</t>
+        </is>
+      </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="n"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -1237,32 +1274,31 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Z7" s="3" t="n"/>
@@ -1282,121 +1318,133 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">458
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t xml:space="preserve">201
+</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1417,126 +1465,122 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n"/>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="n"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">43
+</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="n"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3186
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3822
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="Z9" s="3" t="n"/>
@@ -1554,124 +1598,129 @@
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">424
+</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
-</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5912
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="n"/>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">458
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="R10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n"/>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">488
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">386
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1692,62 +1741,66 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">437
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">421
 </t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n"/>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>942</t>
         </is>
       </c>
       <c r="O11" s="3" t="n"/>
@@ -1759,55 +1812,55 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1828,119 +1881,131 @@
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">1122
+577
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="n"/>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">62
+</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t xml:space="preserve">84
+</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="n"/>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">612
+</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -1961,122 +2026,129 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">183
 </t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="n"/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">627
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="n"/>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -2097,37 +2169,37 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2139,31 +2211,31 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">043
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2175,55 +2247,51 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="n"/>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="Z14" s="3" t="n"/>
@@ -2243,36 +2311,37 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">983
+</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2284,81 +2353,90 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">466
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="n"/>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2379,124 +2457,122 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>923</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9513
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9532
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">922
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">52
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18417
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -2517,113 +2593,132 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">283
+</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="3" t="n"/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="n"/>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">429
+</t>
+        </is>
+      </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">466
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>7043</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">083
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2644,122 +2739,128 @@
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">953
+</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">456
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">686
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4921
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="n"/>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">518
-</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">649
-</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="n"/>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">483
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2780,125 +2881,132 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62622
+</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9812
-</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">942
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="X19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z19" s="3" t="n"/>
@@ -2918,127 +3026,128 @@
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="n"/>
+          <t xml:space="preserve">857
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3059,127 +3168,133 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">392
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2922
+          <t xml:space="preserve">3932
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">9272
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="n"/>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -3200,133 +3315,130 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>381</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">842
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">999
-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="P22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
-</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">084
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">428
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3347,131 +3459,131 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>688</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">3894
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>962</t>
+          <t xml:space="preserve">38
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13932
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>412</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5360
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">379
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4278
+          <t xml:space="preserve">2302
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Z23" s="3" t="n"/>
@@ -3491,122 +3603,125 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2828
+</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">060
+</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
@@ -3631,132 +3746,131 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">446
+</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">978
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">022
+</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">342
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">926
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">21
 </t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3912
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">22 1
 </t>
         </is>
       </c>
@@ -3777,19 +3891,18 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3801,104 +3914,107 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n"/>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">532
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="N26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">632
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="Z26" s="3" t="n"/>
@@ -3918,126 +4034,133 @@
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">19
 </t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">938
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="R27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">393
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">349
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>532</t>
+          <t xml:space="preserve">62
+</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="Z27" s="3" t="n"/>
@@ -4057,43 +4180,43 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">391
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4105,83 +4228,85 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">9584
-</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8539
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">145
 </t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="Z28" s="3" t="n"/>
@@ -4201,13 +4326,13 @@
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">327
+</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">539
 </t>
         </is>
       </c>
@@ -4219,114 +4344,115 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6511
+          <t xml:space="preserve">6825
 </t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4516
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">64
+</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">042
-</t>
-        </is>
-      </c>
-      <c r="W29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z29" s="3" t="n"/>
@@ -4346,49 +4472,54 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">3061
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">43
+</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>588</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>896</t>
+          <t xml:space="preserve">120
+</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>05</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -4400,70 +4531,71 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">39086
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>264</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9222
+          <t xml:space="preserve">3222
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1346
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">10426
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">3225
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -4484,124 +4616,128 @@
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">21
 </t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
+      <c r="M31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7511
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t xml:space="preserve">4526
+</t>
+        </is>
+      </c>
+      <c r="P31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">397
+</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t>26444</t>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">635
 </t>
         </is>
       </c>
@@ -4622,73 +4758,90 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t xml:space="preserve">47
+</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">36
+</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>725</t>
+          <t xml:space="preserve">09
+</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="M32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1289
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">782
+</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
+          <t>264</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4700,37 +4853,37 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">353
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -4749,100 +4902,98 @@
         </is>
       </c>
       <c r="C33" s="3" t="n"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39326
-</t>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>343</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">818
+          <t>125</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">903
-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="n"/>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
@@ -4854,25 +5005,25 @@
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -4890,77 +5041,88 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">782
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9282
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4972,19 +5134,18 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">632
 </t>
         </is>
       </c>
@@ -4996,25 +5157,25 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -5035,128 +5196,121 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="n"/>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">922
 </t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9282
-</t>
-        </is>
-      </c>
+      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>801</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="R35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="n"/>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">451
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -5174,68 +5328,80 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+3
+</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80902
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="n"/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">10
@@ -5248,51 +5414,51 @@
 </t>
         </is>
       </c>
-      <c r="R36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t>283</t>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="inlineStr">
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">283
 </t>
         </is>
       </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="W36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="X36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">676
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n"/>
@@ -5312,68 +5478,75 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3929
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>846344</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">13
+</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14418
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09502
-</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="n"/>
+          <t xml:space="preserve">94503
+</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1428
@@ -5382,54 +5555,56 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t xml:space="preserve">122
+</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">903
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">12421
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">2672
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">324
+</t>
         </is>
       </c>
       <c r="Z37" s="3" t="n"/>
@@ -5447,67 +5622,62 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>4212</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">615
+</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
-        </is>
-      </c>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t>83384</t>
-        </is>
-      </c>
+          <t xml:space="preserve">857
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -5525,56 +5695,54 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="W38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Z38" s="3" t="n"/>
@@ -5594,48 +5762,47 @@
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">516
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">546
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5645,10 +5812,14 @@
 </t>
         </is>
       </c>
-      <c r="M39" s="3" t="n"/>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -5661,13 +5832,13 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5679,7 +5850,7 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -5691,25 +5862,25 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5727,131 +5898,135 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422
+</t>
+        </is>
+      </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">941
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">948
-</t>
-        </is>
-      </c>
-      <c r="N40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">983
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="n"/>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">43
+</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5869,52 +6044,57 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">422
+</t>
+        </is>
+      </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5924,35 +6104,45 @@
 </t>
         </is>
       </c>
-      <c r="M41" s="3" t="n"/>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="n"/>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5964,25 +6154,25 @@
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
@@ -6006,63 +6196,58 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">941
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -6072,64 +6257,69 @@
 </t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9221
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">931
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">720
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="n"/>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="X42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -6153,45 +6343,40 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+      <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -6207,33 +6392,55 @@
 </t>
         </is>
       </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">789
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1142
+745
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225778
+22
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="n"/>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n"/>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">3
+6
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3819
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
@@ -6244,25 +6451,25 @@
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
-        </is>
-      </c>
-      <c r="X43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>243</t>
         </is>
       </c>
       <c r="Z43" s="3" t="n"/>
@@ -6280,95 +6487,98 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">293
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4262
+7
 </t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">020
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">442
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">7
+</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">2429
+14
+</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">7
+7
 </t>
         </is>
       </c>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3663
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77 777
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="n"/>
-      <c r="P44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">069
-</t>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>1065</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
-</t>
-        </is>
-      </c>
-      <c r="R44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="n"/>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6378,16 +6588,15 @@
 </t>
         </is>
       </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">822
+      <c r="X44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>504</t>
         </is>
       </c>
       <c r="Z44" s="3" t="n"/>
@@ -6407,7 +6616,7 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -6419,35 +6628,36 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1929
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">698
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>455</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">2828
 </t>
         </is>
       </c>
@@ -6463,29 +6673,35 @@
 </t>
         </is>
       </c>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">983
-</t>
-        </is>
-      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41272728
+1 8
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">06
 </t>
         </is>
       </c>
-      <c r="Q45" s="3" t="n"/>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -6500,7 +6716,7 @@
       <c r="W45" s="3" t="n"/>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 2
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
@@ -6519,7 +6735,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 191
+</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">323
@@ -6528,89 +6749,90 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
       <c r="M46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+278
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">062
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="n"/>
+      <c r="R46" s="3" t="n"/>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">8
 </t>
         </is>
       </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="n"/>
+      <c r="T46" s="3" t="n"/>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2901
+</t>
+        </is>
+      </c>
       <c r="V46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">999
 </t>
         </is>
       </c>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9 2
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1501
-</t>
-        </is>
-      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">749
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="n"/>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
@@ -738,7 +738,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
@@ -748,9 +748,9 @@
 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -773,9 +773,9 @@
         </is>
       </c>
       <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
@@ -787,46 +787,50 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">916
 </t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>8518</t>
-        </is>
-      </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="n"/>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
@@ -835,28 +839,18 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="W4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -871,40 +865,34 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -928,89 +916,90 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
+          <t>66</t>
+        </is>
+      </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">072
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="W5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="X5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="n"/>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1027,135 +1016,132 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">342
+</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">916
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="S6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">072
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>615</t>
+          <t xml:space="preserve">2074
+</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">513
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="n"/>
+          <t xml:space="preserve">772
+</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -1169,136 +1155,126 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-1
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">322
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t xml:space="preserve">106
+</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">316
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>013</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="n"/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="X7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="Z7" s="3" t="n"/>
@@ -1318,134 +1294,123 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">458
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">946
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="Z8" s="3" t="n"/>
@@ -1465,121 +1430,122 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1474
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">1125
+</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">9578
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">096
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">9492
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="n"/>
+          <t xml:space="preserve">926
+</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14546
+</t>
+        </is>
+      </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="n"/>
+          <t xml:space="preserve">1294
+</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11109
+</t>
+        </is>
+      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">3186
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">19488
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1269
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="n"/>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">2311
 </t>
         </is>
       </c>
@@ -1598,15 +1564,15 @@
         </is>
       </c>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">424
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1618,113 +1584,108 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">972
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">458
-</t>
-        </is>
-      </c>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>521</t>
+          <t xml:space="preserve">912
+</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="n"/>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">1642
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2822
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">386
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="n"/>
+          <t xml:space="preserve">2162
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1741,126 +1702,120 @@
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
-</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
+          <t>483</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>93</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>942</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="S11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1612
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="X11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
@@ -1881,131 +1836,121 @@
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1122
-577
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n"/>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="n"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">251
 </t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">1612
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1945
 </t>
         </is>
       </c>
@@ -2026,129 +1971,116 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">104
+</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>938</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="S13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">627
+          <t>464</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
-</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t>812</t>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1852
 </t>
         </is>
       </c>
@@ -2169,128 +2101,126 @@
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">495
+</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t>3414</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="R14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9234
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">582
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">264
 </t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">514
 </t>
         </is>
       </c>
@@ -2311,55 +2241,48 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">983
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">921
+          <t>08</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -2369,74 +2292,70 @@
 </t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+      <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="R15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">466
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">382
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -2457,122 +2376,124 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1408
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
+          <t xml:space="preserve">946
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">11823
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">19492
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">11246
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">17088
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">11510
 </t>
         </is>
       </c>
@@ -2593,132 +2514,113 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">895
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1912
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">649
+</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="n"/>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">429
-</t>
-        </is>
-      </c>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">466
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">853
-</t>
-        </is>
-      </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2739,128 +2641,120 @@
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>302</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>466</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">456
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="n"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">686
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2288
+</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">072
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="n"/>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">260
+</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4921
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2879,133 +2773,113 @@
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9505
+</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">241
 </t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62622
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="R19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -3026,51 +2900,45 @@
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>486</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
@@ -3078,76 +2946,68 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">857
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="3" t="n"/>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>324</t>
+          <t xml:space="preserve">262
+</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3168,133 +3028,122 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">013
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3932
-</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9272
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -3315,130 +3164,128 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>381</t>
+          <t xml:space="preserve">298
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">842
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="n"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="R22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">399
+</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">9562
+</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">399
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1947
 </t>
         </is>
       </c>
@@ -3459,131 +3306,117 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">11441
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">2904
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n"/>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3894
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">024644
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13932
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14209
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">9316
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">11210
+</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">1072
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">93606
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">11084
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1977
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
+          <t xml:space="preserve">09278
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="Z23" s="3" t="n"/>
@@ -3603,125 +3436,106 @@
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
+</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8298
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2828
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">060
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">939
-</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>3164</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n"/>
+      <c r="O24" s="3" t="n"/>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t>3605</t>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="S24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">7282
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
@@ -3746,131 +3560,129 @@
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">446
-</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">94
 </t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>962</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>934</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="n"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">022
-</t>
-        </is>
-      </c>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
+          <t xml:space="preserve">11922
+</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">090
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>430</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22 1
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -3891,18 +3703,19 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>2951</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -3914,106 +3727,98 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">532
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">7162
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="X26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4034,73 +3839,68 @@
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -4111,55 +3911,50 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="n"/>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="X27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -4180,132 +3975,126 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">327
+</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">079
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">391
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>463</t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">687
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="n"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1190809
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8539
+          <t xml:space="preserve">402
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>537</t>
+          <t xml:space="preserve">538
+</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -4326,13 +4115,13 @@
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -4344,67 +4133,62 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6825
-</t>
-        </is>
-      </c>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">958
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="n"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -4414,27 +4198,27 @@
 </t>
         </is>
       </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="V29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">394
 </t>
         </is>
       </c>
@@ -4444,7 +4228,7 @@
 </t>
         </is>
       </c>
-      <c r="X29" s="3" t="inlineStr">
+      <c r="X29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">862
 </t>
@@ -4452,7 +4236,8 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="Z29" s="3" t="n"/>
@@ -4472,130 +4257,122 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3061
+          <t xml:space="preserve">194984
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">313
+</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">2927
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39086
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3222
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11123
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
+          <t xml:space="preserve">1538222
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1346
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10426
+          <t xml:space="preserve">11042
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3225
+          <t xml:space="preserve">3126
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">9284
 </t>
         </is>
       </c>
@@ -4616,128 +4393,116 @@
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>582</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>806</t>
+          <t xml:space="preserve">161
+</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="M31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7511
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4526
-</t>
-        </is>
-      </c>
-      <c r="P31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
-      <c r="R31" s="3" t="inlineStr">
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">826
+</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">253
 </t>
         </is>
       </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="W31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -4758,135 +4523,124 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">328
+</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4183
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">782
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">12196
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">845
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="n"/>
       <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -4904,73 +4658,70 @@
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>343</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">253
+</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">945
+</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="M33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">879
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -4981,49 +4732,49 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="X33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">803
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1688
 </t>
         </is>
       </c>
@@ -5041,88 +4792,67 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">782
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="3" t="n"/>
+      <c r="O34" s="3" t="n"/>
+      <c r="P34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2825
 </t>
         </is>
       </c>
@@ -5134,40 +4864,40 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="X34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">863
 </t>
@@ -5175,7 +4905,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5196,121 +4926,123 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="N35" s="8" t="inlineStr">
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="n"/>
+      <c r="N35" s="3" t="n"/>
+      <c r="O35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">922
 </t>
         </is>
       </c>
-      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>801</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="n"/>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>246</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">451
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">517
+</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="X35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5328,111 +5060,100 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-3
-</t>
-        </is>
-      </c>
+      <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">514
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2312
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="S36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">283
 </t>
@@ -5440,25 +5161,26 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">582
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="X36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="Z36" s="3" t="n"/>
@@ -5478,132 +5200,127 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
+          <t xml:space="preserve">11615
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">0694
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">87110
+</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">9811
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94503
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9410
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">9506
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1428
 </t>
         </is>
       </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">2413
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12421
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2672
+          <t xml:space="preserve">3672
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">372
 </t>
         </is>
       </c>
@@ -5622,121 +5339,117 @@
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">615
-</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">515
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">492
-</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">857
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">941
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">269
+</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">489
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="W38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2749
+</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5760,49 +5473,49 @@
         </is>
       </c>
       <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">546
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24516
+</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">791
+</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
@@ -5812,34 +5525,33 @@
 </t>
         </is>
       </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="n"/>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -5850,37 +5562,36 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">19482
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -5898,135 +5609,130 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
+      <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">819
+</t>
+        </is>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="n"/>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">070
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="n"/>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">923
+</t>
+        </is>
+      </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t xml:space="preserve">270
+</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">478
+          <t xml:space="preserve">398
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -6044,135 +5750,125 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">325
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0856
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="R41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0820
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6197,135 +5893,123 @@
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">318
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">544
+</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">931
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">2662
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="n"/>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">916
+</t>
+        </is>
+      </c>
+      <c r="S42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">492
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">963
+</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2221
+</t>
+        </is>
+      </c>
+      <c r="W42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">603
 </t>
         </is>
       </c>
       <c r="X42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">02712
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">2167
 </t>
         </is>
       </c>
@@ -6344,134 +6028,28 @@
         </is>
       </c>
       <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">324
-</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1142
-745
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225778
-22
-</t>
-        </is>
-      </c>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="n"/>
+      <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-6
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">953
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">852
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
+      <c r="P43" s="3" t="n"/>
+      <c r="Q43" s="3" t="n"/>
+      <c r="R43" s="3" t="n"/>
+      <c r="S43" s="3" t="n"/>
+      <c r="T43" s="3" t="n"/>
+      <c r="U43" s="3" t="n"/>
+      <c r="V43" s="3" t="n"/>
+      <c r="W43" s="3" t="n"/>
+      <c r="X43" s="3" t="n"/>
+      <c r="Y43" s="3" t="n"/>
       <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -6487,118 +6065,28 @@
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4262
-7
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2429
-14
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-7
-</t>
-        </is>
-      </c>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
       <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77 777
-</t>
-        </is>
-      </c>
+      <c r="N44" s="3" t="n"/>
       <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
-      <c r="S44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
-        </is>
-      </c>
+      <c r="P44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
+      <c r="R44" s="3" t="n"/>
+      <c r="S44" s="3" t="n"/>
       <c r="T44" s="3" t="n"/>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>504</t>
-        </is>
-      </c>
+      <c r="U44" s="3" t="n"/>
+      <c r="V44" s="3" t="n"/>
+      <c r="W44" s="3" t="n"/>
+      <c r="X44" s="3" t="n"/>
+      <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -6616,7 +6104,7 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
@@ -6628,99 +6116,107 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1929
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
+          <t xml:space="preserve">1175
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2828
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1909
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="n"/>
+      <c r="L45" s="3" t="n"/>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41272728
-1 8
-</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="n"/>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="n"/>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="T45" s="3" t="n"/>
+          <t xml:space="preserve">1605
+</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="n"/>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
+</t>
+        </is>
+      </c>
       <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -6737,102 +6233,47 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 191
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">323
-</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-278
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">062
-</t>
-        </is>
-      </c>
+      <c r="M46" s="3" t="n"/>
+      <c r="N46" s="3" t="n"/>
+      <c r="O46" s="3" t="n"/>
+      <c r="P46" s="3" t="n"/>
       <c r="Q46" s="3" t="n"/>
       <c r="R46" s="3" t="n"/>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n"/>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2901
-</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">999
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">749
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n"/>
+      <c r="U46" s="3" t="n"/>
+      <c r="V46" s="3" t="n"/>
+      <c r="W46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2110
+</t>
+        </is>
+      </c>
+      <c r="X46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98855
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1165608
+</t>
+        </is>
+      </c>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
@@ -748,9 +748,9 @@
 </t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
@@ -762,7 +762,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -772,10 +772,15 @@
 </t>
         </is>
       </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">829
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -787,19 +792,19 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -811,7 +816,8 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>326</t>
+          <t xml:space="preserve">306
+</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -822,13 +828,14 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t xml:space="preserve">452
+</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -868,13 +875,13 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -886,19 +893,19 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -916,13 +923,13 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -934,15 +941,17 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>314</t>
+          <t xml:space="preserve">994
+</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="Q5" s="8" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">239
 </t>
@@ -956,7 +965,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -968,22 +977,23 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="X5" s="8" t="inlineStr">
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="W5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">299
 </t>
@@ -991,13 +1001,14 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t xml:space="preserve">68
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1016,11 +1027,11 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
-</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+          <t xml:space="preserve">382
+</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">170
 </t>
@@ -1028,13 +1039,13 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -1044,7 +1055,12 @@
 </t>
         </is>
       </c>
-      <c r="I6" s="3" t="n"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">44
@@ -1053,74 +1069,79 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">144
 </t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2074
-</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">513
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">413
 </t>
         </is>
       </c>
@@ -1138,7 +1159,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1156,9 +1177,9 @@
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -1170,7 +1191,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1180,9 +1201,9 @@
 </t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
@@ -1204,7 +1225,7 @@
 </t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">203
 </t>
@@ -1212,15 +1233,21 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>013</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1237,22 +1264,17 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n"/>
       <c r="V7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -1267,7 +1289,7 @@
       </c>
       <c r="X7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -1277,7 +1299,12 @@
 </t>
         </is>
       </c>
-      <c r="Z7" s="3" t="n"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1298,7 +1325,7 @@
 </t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">184
 </t>
@@ -1306,7 +1333,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -1324,18 +1351,20 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1353,13 +1382,14 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">080
+</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1368,7 +1398,7 @@
 </t>
         </is>
       </c>
-      <c r="R8" s="8" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">223
 </t>
@@ -1382,7 +1412,8 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>662</t>
+          <t xml:space="preserve">662
+</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1391,9 +1422,9 @@
 </t>
         </is>
       </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">946
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1405,15 +1436,22 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="n"/>
+          <t xml:space="preserve">592
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1436,43 +1474,43 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9578
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">096
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9492
+          <t xml:space="preserve">471
 </t>
         </is>
       </c>
@@ -1488,10 +1526,15 @@
 </t>
         </is>
       </c>
-      <c r="N9" s="3" t="n"/>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1001
+</t>
+        </is>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14546
+          <t xml:space="preserve">4516
 </t>
         </is>
       </c>
@@ -1509,13 +1552,14 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11109
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1526,27 +1570,31 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19488
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
-        </is>
-      </c>
-      <c r="X9" s="3" t="n"/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2311
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="Z9" s="3" t="n"/>
@@ -1572,32 +1620,37 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n"/>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">51
+</t>
+        </is>
+      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">19
 </t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">972
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8604
 </t>
         </is>
       </c>
@@ -1610,10 +1663,16 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -1622,8 +1681,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1646,13 +1704,13 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1662,27 +1720,27 @@
 </t>
         </is>
       </c>
-      <c r="W10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2822
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2162
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -1708,17 +1766,17 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">105
 </t>
@@ -1726,20 +1784,26 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="n"/>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>483</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
@@ -1748,18 +1812,24 @@
 </t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>93</t>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -1768,54 +1838,55 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="S11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">657
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="X11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -1833,14 +1904,19 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
 </t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">183
 </t>
@@ -1854,13 +1930,13 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -1872,76 +1948,88 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">672
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">218
 </t>
         </is>
       </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1612
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
@@ -1950,11 +2038,16 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1945
-</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="n"/>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1645
+</t>
+        </is>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1977,45 +2070,61 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -2027,19 +2136,20 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>464</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -2056,7 +2166,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2072,7 +2182,7 @@
 </t>
         </is>
       </c>
-      <c r="X13" s="8" t="inlineStr">
+      <c r="X13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -2080,11 +2190,16 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1852
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -2098,7 +2213,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 3 3 1
+</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -2113,13 +2233,13 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -2143,54 +2263,61 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t>3414</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">814
+</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
 </t>
         </is>
       </c>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9234
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -2202,7 +2329,7 @@
       </c>
       <c r="V14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -2220,11 +2347,16 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
-</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9514
+</t>
+        </is>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -2239,21 +2371,22 @@
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8919
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">295
+</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2264,20 +2397,26 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -2288,26 +2427,31 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="n"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2319,47 +2463,52 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">095
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="n"/>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -2394,12 +2543,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">481
+</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2411,14 +2561,20 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="n"/>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">9513
+</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -2429,29 +2585,31 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t xml:space="preserve">94552
+</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11823
+          <t xml:space="preserve">11829
 </t>
         </is>
       </c>
@@ -2463,37 +2621,32 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">213142
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19492
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11585
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11246
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17088
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">112746
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="n"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11510
+          <t xml:space="preserve">1005
 </t>
         </is>
       </c>
@@ -2511,22 +2664,27 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">895
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -2536,60 +2694,70 @@
 </t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -2607,14 +2775,19 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">222 3
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">215
 </t>
         </is>
       </c>
-      <c r="W17" s="3" t="n"/>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -2639,14 +2812,15 @@
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>302</t>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">089
+</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -2664,18 +2838,19 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>466</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2687,33 +2862,39 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="N18" s="3" t="n"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2288
-</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">072
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="n"/>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">232
+</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -2724,17 +2905,17 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
@@ -2742,13 +2923,13 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -2775,7 +2956,7 @@
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">9505
+          <t xml:space="preserve">097
 </t>
         </is>
       </c>
@@ -2799,34 +2980,50 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="n"/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="n"/>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4183
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -2835,7 +3032,7 @@
 </t>
         </is>
       </c>
-      <c r="R19" s="8" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -2843,43 +3040,43 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">230
 </t>
         </is>
       </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -2897,10 +3094,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">853
+</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2917,13 +3120,14 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>486</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -2934,11 +3138,17 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="8" t="inlineStr">
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">192
 </t>
@@ -2946,21 +3156,26 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -2978,36 +3193,37 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -3028,7 +3244,7 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -3040,19 +3256,19 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">013
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3070,26 +3286,32 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">184
 </t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
       <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3099,9 +3321,9 @@
 </t>
         </is>
       </c>
-      <c r="R21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3113,19 +3335,19 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -3135,15 +3357,10 @@
 </t>
         </is>
       </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
+      <c r="X21" s="3" t="n"/>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -3164,19 +3381,19 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3188,19 +3405,19 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -3210,7 +3427,7 @@
 </t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -3218,20 +3435,25 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="n"/>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3241,9 +3463,9 @@
 </t>
         </is>
       </c>
-      <c r="R22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">399
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3255,28 +3477,28 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9562
-</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">8562
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">802
@@ -3285,7 +3507,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1947
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
@@ -3303,33 +3525,48 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11441
+          <t xml:space="preserve">19446
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2904
+          <t xml:space="preserve">9104
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n"/>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
+</t>
+        </is>
+      </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n"/>
+          <t xml:space="preserve">2208
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">725
+</t>
+        </is>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
@@ -3338,25 +3575,26 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">024644
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t xml:space="preserve">939
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14209
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9316
+          <t xml:space="preserve">9312
 </t>
         </is>
       </c>
@@ -3368,7 +3606,7 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11210
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -3380,36 +3618,37 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93606
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11084
+          <t xml:space="preserve">479
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
+          <t xml:space="preserve">1086
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">1974
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09278
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -3434,27 +3673,27 @@
         </is>
       </c>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">819
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">825
+</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8298
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">914
 </t>
         </is>
       </c>
@@ -3466,11 +3705,16 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0589
+</t>
+        </is>
+      </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3480,14 +3724,20 @@
       </c>
       <c r="M24" s="8" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 312
+</t>
+        </is>
+      </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3499,19 +3749,19 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="S24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7282
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3521,24 +3771,19 @@
 </t>
         </is>
       </c>
-      <c r="V24" s="3" t="inlineStr">
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">817
+</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">205
 </t>
         </is>
       </c>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">852
-</t>
-        </is>
-      </c>
+      <c r="X24" s="3" t="n"/>
       <c r="Y24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">25
@@ -3566,9 +3811,9 @@
 </t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3586,13 +3831,13 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -3604,7 +3849,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3616,20 +3861,20 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="n"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11922
-</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3641,7 +3886,8 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3652,37 +3898,37 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="X25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">678
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">591
 </t>
         </is>
       </c>
@@ -3703,13 +3949,13 @@
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3733,7 +3979,8 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">12
+</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3742,29 +3989,39 @@
 </t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n"/>
-      <c r="N26" s="3" t="n"/>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">926
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 18
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">7 91
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3776,19 +4033,18 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">479
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7162
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -3810,7 +4066,7 @@
 </t>
         </is>
       </c>
-      <c r="X26" s="8" t="inlineStr">
+      <c r="X26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">862
 </t>
@@ -3836,14 +4092,19 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">273
 </t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">974
 </t>
@@ -3863,7 +4124,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3881,7 +4142,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -3893,14 +4154,20 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="n"/>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>494</t>
+          <t xml:space="preserve">48
+</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3917,7 +4184,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -3929,24 +4196,24 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">632
+</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">109
 </t>
         </is>
       </c>
-      <c r="U27" s="3" t="n"/>
       <c r="V27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="X27" s="8" t="inlineStr">
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="n"/>
+      <c r="X27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">802
 </t>
@@ -3954,7 +4221,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -3975,13 +4242,13 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">079
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -3991,13 +4258,13 @@
 </t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
 </t>
@@ -4005,7 +4272,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -4017,31 +4284,37 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">687
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="n"/>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190809
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -4053,13 +4326,14 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t>256</t>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">740
+</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -4070,31 +4344,31 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -4119,7 +4393,7 @@
 </t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">184
 </t>
@@ -4127,62 +4401,66 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">112
 </t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">892
-</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">958
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n"/>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>403</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4212,23 +4490,23 @@
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">394
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">862
 </t>
@@ -4236,7 +4514,7 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4254,10 +4532,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194984
+          <t xml:space="preserve">19484
 </t>
         </is>
       </c>
@@ -4287,92 +4570,98 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2927
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">451
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">9207
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11123
-</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="n"/>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1264
+</t>
+        </is>
+      </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1538222
+          <t xml:space="preserve">33222
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">10881
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11042
+          <t xml:space="preserve">11841
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126
+          <t xml:space="preserve">1084
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9284
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
@@ -4391,15 +4680,15 @@
         </is>
       </c>
       <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">297
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4411,7 +4700,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -4423,23 +4712,35 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">21
+</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -4448,61 +4749,61 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">649
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">773
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -4523,30 +4824,32 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4183
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4557,7 +4860,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4579,10 +4882,15 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="3" t="n"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12196
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4600,7 +4908,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -4612,31 +4920,31 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">2881
+</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">842
 </t>
         </is>
       </c>
@@ -4655,7 +4963,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">326
@@ -4664,19 +4977,19 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4688,33 +5001,43 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
@@ -4744,29 +5067,29 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">486
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="X33" s="8" t="inlineStr">
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">803
 </t>
@@ -4774,7 +5097,7 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
+          <t xml:space="preserve">1658
 </t>
         </is>
       </c>
@@ -4792,10 +5115,15 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">921
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -4805,9 +5133,9 @@
 </t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4825,19 +5153,19 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -4847,18 +5175,33 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
-      <c r="O34" s="3" t="n"/>
-      <c r="P34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2825
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">511
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -4876,13 +5219,14 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">90
+</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
@@ -4893,11 +5237,11 @@
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="X34" s="8" t="inlineStr">
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">863
 </t>
@@ -4905,7 +5249,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4926,31 +5270,30 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">004
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4978,11 +5321,21 @@
 </t>
         </is>
       </c>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">301
+</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">9942
 </t>
         </is>
       </c>
@@ -5012,19 +5365,19 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">517
-</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -5034,7 +5387,7 @@
 </t>
         </is>
       </c>
-      <c r="X35" s="8" t="inlineStr">
+      <c r="X35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">628
 </t>
@@ -5042,7 +5395,7 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
@@ -5063,7 +5416,7 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">336
 </t>
         </is>
       </c>
@@ -5085,21 +5438,21 @@
 </t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">514
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -5116,28 +5469,33 @@
         </is>
       </c>
       <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="n"/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">4706
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2312
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
@@ -5155,7 +5513,7 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -5171,15 +5529,15 @@
 </t>
         </is>
       </c>
-      <c r="X36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">852
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">557
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -5206,7 +5564,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -5218,46 +5576,52 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0694
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87110
+          <t xml:space="preserve">8180
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">0117
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
+          <t xml:space="preserve">499
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9811
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9410
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n"/>
+          <t xml:space="preserve">7210
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">9506
@@ -5266,7 +5630,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -5278,34 +5642,34 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1170
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1206
+</t>
+        </is>
+      </c>
+      <c r="T37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1010
+</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1241
+</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1110
 </t>
         </is>
       </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2413
-</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1009
-</t>
-        </is>
-      </c>
-      <c r="U37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1248
-</t>
-        </is>
-      </c>
-      <c r="V37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1160
-</t>
-        </is>
-      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1299
@@ -5314,13 +5678,13 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3672
+          <t xml:space="preserve">36722
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
+          <t xml:space="preserve">5372
 </t>
         </is>
       </c>
@@ -5341,7 +5705,8 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -5352,7 +5717,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">515
+          <t xml:space="preserve">5246
 </t>
         </is>
       </c>
@@ -5362,7 +5727,7 @@
 </t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
@@ -5370,38 +5735,44 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">941
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="n"/>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
+          <t xml:space="preserve">507
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5419,25 +5790,25 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2749
-</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -5455,7 +5826,8 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Z38" s="3" t="n"/>
@@ -5473,74 +5845,77 @@
         </is>
       </c>
       <c r="C39" s="3" t="n"/>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24516
-</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">791
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">856
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">29
+</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">682
+</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -5549,9 +5924,10 @@
 </t>
         </is>
       </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t>226</t>
+      <c r="R39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">426
+</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -5562,13 +5938,14 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19482
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
@@ -5585,16 +5962,11 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1144
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="n"/>
       <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -5612,41 +5984,41 @@
       <c r="C40" s="3" t="n"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
-</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">325
+</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
-        </is>
-      </c>
-      <c r="J40" s="8" t="inlineStr">
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">910
 </t>
@@ -5654,25 +6026,31 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>421</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">070
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="N40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
@@ -5682,51 +6060,51 @@
 </t>
         </is>
       </c>
-      <c r="Q40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="R40" s="8" t="inlineStr">
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="S40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">608
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1926
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">398
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">286
 </t>
         </is>
       </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
+      <c r="W40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -5753,19 +6131,19 @@
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0856
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5777,44 +6155,44 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">049
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -5826,25 +6204,25 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="R41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0820
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -5862,13 +6240,13 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5893,126 +6271,113 @@
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1229
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1020
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">544
-</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="n"/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">9502
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2662
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="n"/>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">492
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">963
-</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2221
-</t>
-        </is>
-      </c>
-      <c r="W42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">603
-</t>
-        </is>
-      </c>
-      <c r="X42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02712
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="n"/>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">010
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="n"/>
+      <c r="W42" s="3" t="n"/>
+      <c r="X42" s="3" t="n"/>
+      <c r="Y42" s="3" t="n"/>
       <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -6027,7 +6392,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
@@ -6064,7 +6434,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
@@ -6104,116 +6479,128 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">2666
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="n"/>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">2412
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">5097
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">962
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">8187
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">9663
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>821</t>
+          <t xml:space="preserve">02712
+</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -6231,46 +6618,121 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">937
+</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
       <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n"/>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="n"/>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
       <c r="Q46" s="3" t="n"/>
-      <c r="R46" s="3" t="n"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
       <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2110
-</t>
-        </is>
-      </c>
-      <c r="X46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98855
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">602
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165608
+          <t xml:space="preserve">12111011
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
@@ -738,7 +738,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
@@ -750,7 +750,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -762,7 +762,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -798,13 +798,12 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
@@ -828,14 +827,13 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
-</t>
+          <t>452</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -846,7 +844,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -872,7 +870,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">252
@@ -887,7 +890,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -899,25 +902,24 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -927,21 +929,21 @@
 </t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">994
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -965,7 +967,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -977,19 +979,19 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="V5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="W5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">439
+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -1027,121 +1029,121 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">152
+</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">944
+</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">912
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">272
 </t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">975
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -1153,7 +1155,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1246,11 +1248,11 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">201
 </t>
@@ -1264,17 +1266,22 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="n"/>
+          <t xml:space="preserve">872
+</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -1287,7 +1294,7 @@
 </t>
         </is>
       </c>
-      <c r="X7" s="8" t="inlineStr">
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
@@ -1301,7 +1308,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1318,7 +1325,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1333,7 +1345,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1351,13 +1363,13 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1412,7 +1424,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1424,7 +1436,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1442,13 +1454,13 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1474,7 +1486,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">896
 </t>
         </is>
       </c>
@@ -1486,7 +1498,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
@@ -1504,28 +1516,28 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">471
+          <t xml:space="preserve">9441
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">926
 </t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1001
@@ -1534,8 +1546,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4516
-</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1558,7 +1569,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -1570,13 +1581,13 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">488
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
@@ -1594,7 +1605,8 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>314</t>
+          <t xml:space="preserve">311
+</t>
         </is>
       </c>
       <c r="Z9" s="3" t="n"/>
@@ -1611,7 +1623,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">295
@@ -1630,15 +1647,15 @@
 </t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1648,13 +1665,18 @@
 </t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8604
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">185
@@ -1669,7 +1691,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1710,7 +1732,7 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1740,7 +1762,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -1784,13 +1806,13 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1802,14 +1824,13 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
@@ -1820,16 +1841,11 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="n"/>
       <c r="P11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -1842,33 +1858,33 @@
 </t>
         </is>
       </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">398
-</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">657
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -1880,7 +1896,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -1906,7 +1922,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -1916,7 +1932,7 @@
 </t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">183
 </t>
@@ -1930,13 +1946,13 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -1954,7 +1970,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">046
 </t>
         </is>
       </c>
@@ -1970,7 +1986,7 @@
 </t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="N12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">226
 </t>
@@ -1990,7 +2006,7 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -2002,19 +2018,19 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">672
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2026,7 +2042,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2038,13 +2054,13 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -2076,7 +2092,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -2088,7 +2104,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -2100,7 +2116,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2124,7 +2140,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -2142,7 +2158,7 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -2166,7 +2182,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -2213,12 +2229,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 3 3 1
-</t>
-        </is>
-      </c>
+      <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -2233,7 +2244,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -2243,7 +2254,7 @@
 </t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">165
 </t>
@@ -2275,19 +2286,14 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">814
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -2299,7 +2305,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -2311,13 +2317,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
@@ -2347,13 +2353,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">7172
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9514
+          <t xml:space="preserve">514
 </t>
         </is>
       </c>
@@ -2370,16 +2376,21 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8919
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2403,19 +2414,19 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2427,25 +2438,25 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">915
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">012
 </t>
         </is>
       </c>
@@ -2461,9 +2472,9 @@
 </t>
         </is>
       </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">048
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -2485,9 +2496,9 @@
 </t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">095
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2505,7 +2516,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2525,19 +2536,18 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408
+          <t xml:space="preserve">19404
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>443</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
@@ -2549,7 +2559,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">015
 </t>
         </is>
       </c>
@@ -2561,13 +2571,13 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -2591,7 +2601,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94552
+          <t xml:space="preserve">4532
 </t>
         </is>
       </c>
@@ -2603,13 +2613,13 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1222
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11829
+          <t xml:space="preserve">11273
 </t>
         </is>
       </c>
@@ -2621,32 +2631,32 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213142
+          <t xml:space="preserve">0182
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11585
+          <t xml:space="preserve">9848
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112746
+          <t xml:space="preserve">11246
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="n"/>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1005
+          <t xml:space="preserve">100646
 </t>
         </is>
       </c>
@@ -2664,15 +2674,10 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
+      <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -2684,7 +2689,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -2708,7 +2713,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -2719,18 +2724,13 @@
 </t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">91
@@ -2739,7 +2739,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2751,19 +2751,19 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">353
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222 3
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -2812,39 +2812,38 @@
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">089
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2862,13 +2861,13 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2887,8 +2886,7 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -2905,13 +2903,13 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2923,7 +2921,7 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -2953,10 +2951,15 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">097
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -2980,7 +2983,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>469</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -3001,9 +3004,9 @@
 </t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4183
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3040,19 +3043,19 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -3094,21 +3097,16 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">853
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3156,11 +3154,16 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="n"/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">902
@@ -3187,25 +3190,25 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -3217,7 +3220,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -3244,8 +3247,7 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3262,22 +3264,22 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">19
@@ -3286,7 +3288,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -3317,13 +3319,13 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3335,13 +3337,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -3381,8 +3383,7 @@
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -3391,36 +3392,36 @@
 </t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">328
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">232
 </t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -3435,13 +3436,13 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -3477,7 +3478,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8562
+          <t xml:space="preserve">89562
 </t>
         </is>
       </c>
@@ -3525,58 +3526,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19446
+          <t xml:space="preserve">1944
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3587,23 +3581,22 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n"/>
+          <t xml:space="preserve">929
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9312
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t>431</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1210
@@ -3612,7 +3605,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
@@ -3624,7 +3617,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">3602
 </t>
         </is>
       </c>
@@ -3642,19 +3635,19 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">0949278
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3673,9 +3666,9 @@
         </is>
       </c>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">825
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -3685,15 +3678,15 @@
 </t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">914
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -3705,20 +3698,19 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0589
-</t>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
       <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
@@ -3731,13 +3723,13 @@
       <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 312
+          <t xml:space="preserve">5812
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -3749,19 +3741,19 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="S24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8239
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">782
 </t>
         </is>
       </c>
@@ -3771,9 +3763,9 @@
 </t>
         </is>
       </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
@@ -3804,11 +3796,15 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -3819,56 +3815,50 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="n"/>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3898,8 +3888,7 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
@@ -3910,25 +3899,25 @@
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="X25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">678
+          <t xml:space="preserve">713
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -3947,9 +3936,9 @@
         </is>
       </c>
       <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -3973,7 +3962,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3991,37 +3980,32 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 91
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4033,18 +4017,19 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">239
+</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
@@ -4092,12 +4077,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">273
@@ -4106,7 +4086,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -4124,7 +4104,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4136,13 +4116,13 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -4154,19 +4134,19 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -4178,13 +4158,13 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -4202,11 +4182,11 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
 </t>
@@ -4221,7 +4201,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -4242,13 +4222,13 @@
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4260,7 +4240,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4272,7 +4252,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -4284,37 +4264,36 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">12724
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -4330,9 +4309,9 @@
 </t>
         </is>
       </c>
-      <c r="S28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">740
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
@@ -4344,32 +4323,31 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
+          <t xml:space="preserve">534
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="Z28" s="3" t="n"/>
@@ -4407,7 +4385,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4419,7 +4397,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -4443,19 +4421,14 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="n"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>407</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
@@ -4476,7 +4449,7 @@
 </t>
         </is>
       </c>
-      <c r="S29" s="8" t="inlineStr">
+      <c r="S29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
@@ -4502,7 +4475,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4514,7 +4487,7 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -4532,27 +4505,22 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19484
+          <t xml:space="preserve">1494
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -4582,44 +4550,43 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">961
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9207
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
@@ -4631,37 +4598,36 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33222
+          <t xml:space="preserve">3222
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10881
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11841
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
-</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -4680,21 +4646,21 @@
         </is>
       </c>
       <c r="C31" s="3" t="n"/>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">397
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -4723,9 +4689,9 @@
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -4737,7 +4703,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -4749,7 +4715,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4759,9 +4725,9 @@
 </t>
         </is>
       </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -4773,13 +4739,13 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
+          <t xml:space="preserve">641
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -4803,7 +4769,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -4824,8 +4790,7 @@
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>348</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4836,7 +4801,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -4846,21 +4811,21 @@
 </t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -4872,25 +4837,20 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+      <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
@@ -4908,7 +4868,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -4920,11 +4880,11 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2881
-</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
+          <t xml:space="preserve">352
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">155
 </t>
@@ -4944,7 +4904,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -4963,21 +4923,15 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
+      <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -5001,7 +4955,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5017,30 +4971,25 @@
 </t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="M33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="n"/>
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">598
-</t>
-        </is>
-      </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -5055,7 +5004,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -5067,7 +5016,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">486
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5079,13 +5028,13 @@
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -5097,7 +5046,7 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5115,12 +5064,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
+      <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">321
@@ -5129,7 +5073,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -5159,13 +5103,13 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5175,21 +5119,21 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="N34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">511
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">919
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5201,7 +5145,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5219,13 +5163,13 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -5249,7 +5193,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -5270,19 +5214,20 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">004
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">274
+</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -5293,7 +5238,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -5317,25 +5262,25 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9942
+          <t xml:space="preserve">1724
 </t>
         </is>
       </c>
@@ -5365,7 +5310,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1922
 </t>
         </is>
       </c>
@@ -5377,7 +5322,7 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
@@ -5395,7 +5340,7 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -5416,14 +5361,13 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5434,7 +5378,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5446,13 +5390,13 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -5468,25 +5412,24 @@
 </t>
         </is>
       </c>
-      <c r="M36" s="3" t="n"/>
-      <c r="N36" s="3" t="inlineStr">
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n"/>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4706
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">312
@@ -5495,7 +5438,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -5507,7 +5450,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5531,13 +5474,13 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">557
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -5558,13 +5501,13 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11615
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -5576,61 +5519,61 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">0694
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8180
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0117
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">9499
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7210
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9506
+          <t xml:space="preserve">9502
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -5642,13 +5585,13 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">12304
 </t>
         </is>
       </c>
@@ -5660,13 +5603,13 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -5678,13 +5621,13 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36722
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5372
+          <t xml:space="preserve">372
 </t>
         </is>
       </c>
@@ -5715,19 +5658,19 @@
 </t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5246
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">174
 </t>
@@ -5741,32 +5684,31 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
@@ -5790,7 +5732,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -5808,7 +5750,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -5826,7 +5768,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -5853,62 +5795,62 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">682
-</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">7960
 </t>
         </is>
       </c>
@@ -5924,7 +5866,7 @@
 </t>
         </is>
       </c>
-      <c r="R39" s="8" t="inlineStr">
+      <c r="R39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">426
 </t>
@@ -5938,19 +5880,19 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -5962,7 +5904,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -5996,7 +5938,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -6008,7 +5950,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6020,13 +5962,13 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
@@ -6042,9 +5984,9 @@
 </t>
         </is>
       </c>
-      <c r="N40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -6060,27 +6002,27 @@
 </t>
         </is>
       </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="S40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">608
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">312
+</t>
+        </is>
+      </c>
+      <c r="R40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1926
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -6096,15 +6038,15 @@
 </t>
         </is>
       </c>
-      <c r="W40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">518
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6129,7 +6071,7 @@
         </is>
       </c>
       <c r="C41" s="3" t="n"/>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
@@ -6137,28 +6079,28 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">179 0
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">29
@@ -6167,7 +6109,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -6177,31 +6119,26 @@
 </t>
         </is>
       </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">049
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">992
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="n"/>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">24
@@ -6222,7 +6159,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6234,8 +6171,7 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
@@ -6246,7 +6182,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">682
 </t>
         </is>
       </c>
@@ -6277,27 +6213,27 @@
 </t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -6309,7 +6245,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6319,24 +6255,19 @@
 </t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="M42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9502
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">984
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="n"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">922
@@ -6361,16 +6292,21 @@
 </t>
         </is>
       </c>
-      <c r="S42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="n"/>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">010
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">276
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 14
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -6491,13 +6427,13 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -6509,25 +6445,23 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>056</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">1411
 </t>
         </is>
       </c>
@@ -6539,13 +6473,12 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2666
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -6570,37 +6503,37 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5097
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8187
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9663
+          <t xml:space="preserve">963
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02712
+          <t xml:space="preserve">2212
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -6639,7 +6572,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">937
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -6655,22 +6588,27 @@
 </t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">041
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">427
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -6682,7 +6620,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -6726,13 +6664,13 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12111011
+          <t xml:space="preserve">872085
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
@@ -738,7 +738,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -798,12 +798,13 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -827,13 +828,14 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>452</t>
+          <t xml:space="preserve">45
+</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -844,7 +846,7 @@
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -870,15 +872,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
-</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -890,19 +887,19 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -914,33 +911,34 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -973,19 +971,19 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">439
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -1003,7 +1001,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -1035,11 +1033,11 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
-</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">276
 </t>
@@ -1065,7 +1063,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -1089,19 +1087,19 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">9212
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1125,13 +1123,13 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">3906
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1143,7 +1141,7 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1155,7 +1153,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -1179,7 +1177,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">305
 </t>
@@ -1193,7 +1191,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -1203,9 +1201,9 @@
 </t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">798
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1223,7 +1221,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -1235,14 +1233,18 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="n"/>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">902
 </t>
         </is>
       </c>
@@ -1252,7 +1254,7 @@
 </t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">201
 </t>
@@ -1272,7 +1274,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -1296,19 +1298,19 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">742
+</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1325,12 +1327,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">268
@@ -1345,8 +1342,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1363,7 +1359,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1394,13 +1390,13 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">7912
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1424,7 +1420,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
@@ -1436,7 +1432,7 @@
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -1454,13 +1450,13 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -1480,14 +1476,13 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">1479
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">896
-</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1498,14 +1493,13 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1516,37 +1510,38 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9441
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">39726
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t xml:space="preserve">4512
+</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1563,13 +1558,13 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -1599,17 +1594,21 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">3826
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">311
 </t>
         </is>
       </c>
-      <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1623,12 +1622,7 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 1
-</t>
-        </is>
-      </c>
+      <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">295
@@ -1637,7 +1631,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1647,15 +1641,15 @@
 </t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">916
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1667,13 +1661,13 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -1691,19 +1685,20 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -1726,7 +1721,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -1756,13 +1751,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
@@ -1780,7 +1775,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">290
 </t>
@@ -1794,61 +1789,51 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">105
 </t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>084</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">916
+</t>
+        </is>
+      </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1860,7 +1845,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -1872,8 +1857,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1884,13 +1868,12 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
+          <t>289</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -1906,7 +1889,12 @@
 </t>
         </is>
       </c>
-      <c r="Z11" s="3" t="n"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1920,12 +1908,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
+      <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">264
@@ -1946,19 +1929,19 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">9 841
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1970,13 +1953,13 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">046
+          <t xml:space="preserve">086
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1988,7 +1971,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2000,13 +1983,13 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">084
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2024,13 +2007,13 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -2042,25 +2025,25 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -2086,7 +2069,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2098,7 +2081,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
@@ -2116,7 +2099,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -2128,25 +2111,25 @@
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2182,7 +2165,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -2206,13 +2189,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2229,7 +2212,12 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -2256,7 +2244,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -2268,13 +2256,13 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2286,11 +2274,16 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="n"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">912
@@ -2317,13 +2310,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">582
 </t>
         </is>
       </c>
@@ -2333,9 +2326,9 @@
 </t>
         </is>
       </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -2353,7 +2346,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7172
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -2376,15 +2369,10 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -2394,9 +2382,9 @@
 </t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
@@ -2406,7 +2394,7 @@
 </t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">179
 </t>
@@ -2414,7 +2402,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -2426,8 +2414,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -2444,19 +2431,19 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2472,9 +2459,9 @@
 </t>
         </is>
       </c>
-      <c r="S15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -2492,7 +2479,7 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -2516,7 +2503,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -2536,54 +2523,49 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19404
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">1123
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">015
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9513
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
@@ -2595,31 +2577,31 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4532
+          <t xml:space="preserve">8532
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11273
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -2631,36 +2613,45 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0182
-</t>
+          <t>382</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9848
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11246
-</t>
-        </is>
-      </c>
-      <c r="X16" s="3" t="n"/>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1246
+</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100646
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="n"/>
+          <t xml:space="preserve">9708
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2677,25 +2668,24 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -2713,12 +2703,12 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
@@ -2726,14 +2716,19 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -2743,9 +2738,9 @@
 </t>
         </is>
       </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">518
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -2755,27 +2750,27 @@
 </t>
         </is>
       </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">353
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -2793,11 +2788,16 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2814,49 +2814,45 @@
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
@@ -2871,22 +2867,27 @@
 </t>
         </is>
       </c>
-      <c r="N18" s="3" t="n"/>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">2912
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">0 2
 </t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>892</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
@@ -2903,13 +2904,13 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">542
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2927,17 +2928,21 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">852
+</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="Z18" s="3" t="n"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>11</t>
@@ -2953,13 +2958,13 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
@@ -2971,7 +2976,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2983,12 +2988,13 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>469</t>
+          <t xml:space="preserve">154
+</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3012,11 +3018,16 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">922
@@ -3055,7 +3066,7 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3067,7 +3078,7 @@
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3079,11 +3090,16 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">06
 </t>
         </is>
       </c>
-      <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -3097,16 +3113,21 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 8
+</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3116,9 +3137,9 @@
 </t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">596
 </t>
         </is>
       </c>
@@ -3142,31 +3163,26 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
@@ -3190,13 +3206,13 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -3208,7 +3224,7 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3218,9 +3234,9 @@
 </t>
         </is>
       </c>
-      <c r="X20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3230,7 +3246,11 @@
 </t>
         </is>
       </c>
-      <c r="Z20" s="3" t="n"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -3244,10 +3264,16 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3258,7 +3284,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -3270,7 +3296,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3288,7 +3314,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3319,13 +3345,13 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3337,36 +3363,46 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">887
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">219
 </t>
         </is>
       </c>
-      <c r="X21" s="3" t="n"/>
       <c r="Y21" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">903
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">08
 </t>
         </is>
       </c>
-      <c r="Z21" s="3" t="n"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -3380,21 +3416,27 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>374</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -3418,7 +3460,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -3430,25 +3472,25 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">9912
 </t>
         </is>
       </c>
@@ -3460,13 +3502,13 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3478,7 +3520,7 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89562
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -3490,29 +3532,34 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">226
 </t>
         </is>
       </c>
-      <c r="X22" s="3" t="inlineStr">
+      <c r="Y22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">802
 </t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">947
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -3529,7 +3576,7 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1944
+          <t xml:space="preserve">19426
 </t>
         </is>
       </c>
@@ -3541,36 +3588,37 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t xml:space="preserve">287
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3581,19 +3629,20 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">19529
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>431</t>
+          <t xml:space="preserve">9512
+</t>
         </is>
       </c>
       <c r="P23" s="3" t="n"/>
@@ -3605,53 +3654,58 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3602
+          <t xml:space="preserve">360
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
+          <t xml:space="preserve">377
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
+          <t xml:space="preserve">1084
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1026
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0949278
+          <t xml:space="preserve">1987
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+          <t xml:space="preserve">94256
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3665,7 +3719,12 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">285
@@ -3698,38 +3757,48 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">656
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
-        </is>
-      </c>
-      <c r="M24" s="8" t="inlineStr">
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="N24" s="3" t="n"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5812
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3741,19 +3810,19 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="S24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8239
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">782
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
@@ -3763,7 +3832,7 @@
 </t>
         </is>
       </c>
-      <c r="V24" s="3" t="inlineStr">
+      <c r="V24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">217
 </t>
@@ -3775,14 +3844,24 @@
 </t>
         </is>
       </c>
-      <c r="X24" s="3" t="n"/>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="Z24" s="3" t="n"/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3796,88 +3875,91 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>4441</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1
 </t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="n"/>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -3888,12 +3970,13 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t xml:space="preserve">312
+</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -3905,19 +3988,18 @@
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">713
+          <t>49</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">693
 </t>
         </is>
       </c>
@@ -3935,16 +4017,21 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">986
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1116
+</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -3956,7 +4043,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -3980,26 +4067,31 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n"/>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9896
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -4017,13 +4109,13 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4041,29 +4133,34 @@
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="W26" s="3" t="inlineStr">
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">245
 </t>
         </is>
       </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -4098,7 +4195,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -4110,19 +4207,19 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4134,19 +4231,19 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">9222
 </t>
         </is>
       </c>
@@ -4158,13 +4255,13 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -4182,30 +4279,40 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">214
 </t>
         </is>
       </c>
-      <c r="W27" s="3" t="n"/>
       <c r="X27" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">802
 </t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="n"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -4220,7 +4327,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">327
 </t>
@@ -4228,7 +4335,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4240,7 +4347,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4264,60 +4371,61 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>09</t>
+          <t xml:space="preserve">03
+</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12724
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">500
 </t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">402
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -4329,28 +4437,34 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">534
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>856</t>
-        </is>
-      </c>
-      <c r="Z28" s="3" t="n"/>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">532
+</t>
+        </is>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -4379,31 +4493,31 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4419,21 +4533,22 @@
 </t>
         </is>
       </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n"/>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>407</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4451,7 +4566,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -4469,29 +4584,34 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">201
 </t>
         </is>
       </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Z29" s="3" t="n"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -4508,25 +4628,25 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
+          <t xml:space="preserve">14984
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1896
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4544,32 +4664,32 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">2925
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">961
+          <t xml:space="preserve">3921
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>453</t>
+          <t xml:space="preserve">451
+</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4586,7 +4706,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -4610,28 +4730,33 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1041
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t xml:space="preserve">3122
+</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
-        </is>
-      </c>
-      <c r="Z30" s="3" t="n"/>
+          <t xml:space="preserve">524
+</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4654,7 +4779,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4666,13 +4791,13 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -4684,12 +4809,12 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
-      <c r="L31" s="8" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
@@ -4703,7 +4828,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -4721,25 +4846,25 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">641
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -4751,29 +4876,34 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">773
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
+      <c r="X31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="n"/>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -4787,22 +4917,26 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>348</t>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2328
+</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4813,19 +4947,18 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4835,35 +4968,34 @@
 </t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
+      <c r="L32" s="3" t="n"/>
       <c r="M32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="N32" s="3" t="n"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
@@ -4880,7 +5012,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">352
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -4892,7 +5024,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4904,11 +5036,15 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="n"/>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
       <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -4923,10 +5059,16 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">926
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -4971,7 +5113,7 @@
 </t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -4979,14 +5121,14 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5004,7 +5146,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -5016,41 +5158,46 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">803
+</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">803
-</t>
-        </is>
-      </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -5073,13 +5220,13 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5089,7 +5236,7 @@
 </t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -5109,7 +5256,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5119,9 +5266,9 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">919
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5133,19 +5280,19 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -5163,13 +5310,13 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5193,11 +5340,16 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="n"/>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -5211,7 +5363,12 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">304
@@ -5262,25 +5419,25 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1724
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
@@ -5290,7 +5447,7 @@
 </t>
         </is>
       </c>
-      <c r="Q35" s="3" t="inlineStr">
+      <c r="Q35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">280
 </t>
@@ -5310,7 +5467,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -5344,7 +5501,12 @@
 </t>
         </is>
       </c>
-      <c r="Z35" s="3" t="n"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">336
+</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5359,15 +5521,16 @@
         </is>
       </c>
       <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">336
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t xml:space="preserve">190
+</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5396,7 +5559,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -5408,25 +5571,31 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="M36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n"/>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>707</t>
+          <t xml:space="preserve">902
+</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5436,9 +5605,9 @@
 </t>
         </is>
       </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
+      <c r="R36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">350
 </t>
         </is>
       </c>
@@ -5450,13 +5619,13 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -5474,7 +5643,7 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
@@ -5484,7 +5653,12 @@
 </t>
         </is>
       </c>
-      <c r="Z36" s="3" t="n"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5507,7 +5681,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">19295
 </t>
         </is>
       </c>
@@ -5519,14 +5693,13 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0694
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -5537,7 +5710,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -5549,31 +5722,31 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">9511
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9502
+          <t xml:space="preserve">1502
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -5585,43 +5758,43 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">1173
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12304
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">1013
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">73672
 </t>
         </is>
       </c>
@@ -5631,7 +5804,12 @@
 </t>
         </is>
       </c>
-      <c r="Z37" s="3" t="n"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2473
+</t>
+        </is>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5660,7 +5838,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -5684,31 +5862,32 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>468</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
@@ -5724,7 +5903,7 @@
 </t>
         </is>
       </c>
-      <c r="R38" s="3" t="inlineStr">
+      <c r="R38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">235
 </t>
@@ -5732,47 +5911,52 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">822
+</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">149
 </t>
         </is>
       </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="V38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5789,29 +5973,27 @@
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
+          <t>454</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">170
 </t>
@@ -5819,7 +6001,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5831,17 +6013,17 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
+          <t xml:space="preserve">602
+</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -5850,7 +6032,7 @@
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960
+          <t xml:space="preserve">796
 </t>
         </is>
       </c>
@@ -5868,48 +6050,57 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">426
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">612
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="n"/>
-      <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -5923,7 +6114,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">325
@@ -5938,7 +6134,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
@@ -5950,7 +6146,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -5962,13 +6158,13 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5980,13 +6176,13 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -6002,15 +6198,15 @@
 </t>
         </is>
       </c>
-      <c r="Q40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">312
-</t>
-        </is>
-      </c>
-      <c r="R40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">822
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -6022,22 +6218,22 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">472
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -6046,7 +6242,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6056,7 +6252,12 @@
 </t>
         </is>
       </c>
-      <c r="Z40" s="3" t="n"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8262
+</t>
+        </is>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -6073,13 +6274,13 @@
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179 0
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -6097,14 +6298,13 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -6115,13 +6315,13 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">091
 </t>
         </is>
       </c>
@@ -6134,14 +6334,19 @@
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n"/>
+          <t xml:space="preserve">812
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
@@ -6159,30 +6364,31 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">378
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">212
+</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">682
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6192,7 +6398,12 @@
 </t>
         </is>
       </c>
-      <c r="Z41" s="3" t="n"/>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -6207,33 +6418,28 @@
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">324
 </t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -6243,75 +6449,90 @@
 </t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">728
+</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">922
+</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">86
 </t>
         </is>
       </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">984
-</t>
-        </is>
-      </c>
-      <c r="M42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="n"/>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 14
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="n"/>
-      <c r="W42" s="3" t="n"/>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="X42" s="3" t="n"/>
       <c r="Y42" s="3" t="n"/>
       <c r="Z42" s="3" t="n"/>
@@ -6427,58 +6648,55 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">547
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>698</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>056</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1119
+</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">23662
 </t>
         </is>
       </c>
@@ -6488,10 +6706,15 @@
 </t>
         </is>
       </c>
-      <c r="Q45" s="3" t="n"/>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1069
+</t>
+        </is>
+      </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">1027
 </t>
         </is>
       </c>
@@ -6503,19 +6726,19 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1327
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">8927
 </t>
         </is>
       </c>
@@ -6527,17 +6750,22 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212
+          <t xml:space="preserve">193272
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6554,28 +6782,28 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">255
 </t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">175
@@ -6584,37 +6812,37 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">041
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">427
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6626,55 +6854,65 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="Q46" s="3" t="n"/>
       <c r="R46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">229
 </t>
         </is>
       </c>
-      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">602
 </t>
         </is>
       </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">823
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">872085
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n"/>
+      <c r="Y46" s="3" t="n"/>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 9929
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
@@ -738,122 +738,102 @@
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>914</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="X4" s="3" t="n"/>
@@ -875,140 +855,117 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
-</t>
+          <t>702</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1027,140 +984,117 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">276
-</t>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>276</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1177,64 +1111,54 @@
         </is>
       </c>
       <c r="C7" s="3" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">305
-</t>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>305</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1244,74 +1168,62 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1330,14 +1242,12 @@
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1347,117 +1257,98 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7912
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1476,8 +1367,7 @@
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1479
-</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1487,14 +1377,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1504,92 +1392,77 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39726
-</t>
+          <t>926</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
-</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
-</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3186
-</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
-</t>
+          <t>488</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
@@ -1599,14 +1472,12 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3826
-</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1625,140 +1496,117 @@
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1775,35 +1623,30 @@
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>290</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J11" s="3" t="n"/>
@@ -1813,46 +1656,39 @@
           <t>084</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1862,8 +1698,7 @@
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
@@ -1871,28 +1706,24 @@
           <t>289</t>
         </is>
       </c>
-      <c r="W11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>229</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1911,140 +1742,117 @@
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 841
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">086
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2063,140 +1871,117 @@
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>842</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2214,146 +1999,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1 01</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">514
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2372,44 +2133,37 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">935
-</t>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>295</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -2419,92 +2173,77 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2523,20 +2262,17 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2546,69 +2282,58 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>875</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>1222</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -2618,38 +2343,32 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
-</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9708
-</t>
+          <t>088</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2665,17 +2384,19 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -2685,117 +2406,98 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>199</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2834,20 +2536,17 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2857,32 +2556,27 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 2
-</t>
+          <t>0 2</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -2892,38 +2586,32 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">542
-</t>
+          <t>542</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
@@ -2933,14 +2621,12 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>852</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2958,146 +2644,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>878</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3115,135 +2777,113 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
+          <t>1 01</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">596
-</t>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N20" s="3" t="n"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>992</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">232
-</t>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>852</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -3266,141 +2906,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="n"/>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">887
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3418,146 +3039,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>562</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3576,20 +3173,17 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19426
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3599,111 +3193,93 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>838</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19529
-</t>
+          <t>929</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9512
-</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="P23" s="3" t="n"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">377
-</t>
+          <t>377</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
-</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1026
-</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1987
-</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94256
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3721,44 +3297,37 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -3768,98 +3337,82 @@
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
-</t>
+          <t>9919991</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>217</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3878,20 +3431,17 @@
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3901,14 +3451,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3918,38 +3466,32 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -3964,26 +3506,22 @@
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>712</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
@@ -3993,14 +3531,12 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">693
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="Z25" s="3" t="n"/>
@@ -4019,146 +3555,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9896
-</t>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>299</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4177,140 +3689,117 @@
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9222
-</t>
+          <t>982</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4327,142 +3816,119 @@
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">327
-</t>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>327</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>402</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4481,135 +3947,113 @@
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M29" s="3" t="n"/>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4628,44 +4072,37 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14984
-</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1896
-</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>588</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
-</t>
+          <t>806</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4675,81 +4112,68 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3921
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">451
-</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
-</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
-</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3222
-</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3122
-</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4773,135 +4197,113 @@
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="X31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">478
-</t>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>778</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4919,14 +4321,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2328
-</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>388</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4941,14 +4341,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4958,39 +4356,33 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="L32" s="3" t="n"/>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -5000,38 +4392,32 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>358</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
@@ -5041,8 +4427,7 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="Z32" s="3" t="n"/>
@@ -5061,141 +4446,118 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>946</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>782</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">803
-</t>
+          <t>802</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5211,143 +4573,124 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>672</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5365,146 +4708,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>280</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5521,142 +4840,119 @@
         </is>
       </c>
       <c r="C36" s="3" t="n"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">336
-</t>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>936</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">902
-</t>
+          <t>902</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
-        </is>
-      </c>
-      <c r="R36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">350
-</t>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>250</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
-</t>
+          <t>552</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5675,26 +4971,22 @@
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
-</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19295
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -5704,110 +4996,92 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9499
-</t>
+          <t>491</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9511
-</t>
+          <t>951</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1502
-</t>
+          <t>502</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>1428</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1173
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
-</t>
+          <t>703</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
-</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73672
-</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">372
-</t>
+          <t>372</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2473
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5826,135 +5100,117 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>923</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
-</t>
+          <t>909</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="R38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>235</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5973,8 +5229,7 @@
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -5984,8 +5239,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -5993,95 +5247,80 @@
           <t>454</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241 7</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -6091,14 +5330,12 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6116,146 +5353,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
-</t>
+          <t>472</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8262
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6274,32 +5487,27 @@
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -6309,99 +5517,83 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">091
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>201</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
-</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">378
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6421,116 +5613,97 @@
       <c r="D42" s="3" t="n"/>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">728
-</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="X42" s="3" t="n"/>
@@ -6551,8 +5724,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D43" s="3" t="n"/>
@@ -6593,8 +5765,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6636,26 +5807,22 @@
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
-</t>
+          <t>547</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -6665,105 +5832,88 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23662
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1069
-</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1027
-</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2412
-</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1327
-</t>
+          <t>387</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>953</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8927
-</t>
+          <t>857</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">963
-</t>
+          <t>963</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193272
-</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -6782,135 +5932,113 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="J46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">307
-</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>137</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 9929
-</t>
+          <t>0 22</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -788,12 +779,12 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>211</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -808,7 +799,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>298</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -818,7 +809,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>452</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -865,7 +856,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>218</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -905,7 +896,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>201</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -930,7 +921,7 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>281</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -940,7 +931,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
@@ -994,7 +985,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1019,7 +1010,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1034,7 +1025,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>128</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1089,7 +1080,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>372</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -1188,7 +1179,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1293,7 +1284,7 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
@@ -1397,7 +1388,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1462,7 +1453,7 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
@@ -1511,12 +1502,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>196</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1546,12 +1537,12 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>2913</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1576,7 +1567,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>642</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1646,7 +1637,7 @@
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J11" s="3" t="n"/>
@@ -1757,7 +1748,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>2 81</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1792,7 +1783,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -1807,7 +1798,7 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1876,7 +1867,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1921,7 +1912,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -1951,7 +1942,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>742</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -1976,7 +1967,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -1999,7 +1990,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>1 01</t>
+          <t>0 1 01</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2024,7 +2015,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>165</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -2039,7 +2030,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -2054,7 +2045,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2079,12 +2070,12 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>582</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
@@ -2109,7 +2100,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -2158,7 +2149,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -2183,7 +2174,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -2208,7 +2199,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>107</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -2238,12 +2229,12 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>03</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2272,7 +2263,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2282,7 +2273,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>815</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2292,7 +2283,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>173</t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
@@ -2313,7 +2304,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>1532</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2323,12 +2314,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -2343,17 +2334,17 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>412</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2363,7 +2354,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>088</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2386,7 +2377,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2421,23 +2412,23 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>221</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2457,7 +2448,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>125</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -2487,7 +2478,7 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>249</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -2536,7 +2527,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>166</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -2561,12 +2552,12 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2601,12 +2592,12 @@
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>101</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -2644,7 +2635,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2699,7 +2690,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -2754,7 +2745,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>812</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2777,7 +2768,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>1 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2797,7 +2788,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>296</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2812,7 +2803,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2843,7 +2834,7 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -2853,7 +2844,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>297</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -2863,7 +2854,7 @@
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>109</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
@@ -2878,7 +2869,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -2906,12 +2897,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>289</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2981,7 +2972,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>191</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -2991,7 +2982,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>282</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -3011,7 +3002,7 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>219</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -3039,7 +3030,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3094,7 +3085,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3129,7 +3120,7 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
@@ -3173,7 +3164,7 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3183,7 +3174,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3208,12 +3199,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>317</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -3223,12 +3214,12 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="P23" s="3" t="n"/>
@@ -3244,17 +3235,17 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>347</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3269,12 +3260,12 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
@@ -3327,7 +3318,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -3335,9 +3326,9 @@
           <t>18</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
-        <is>
-          <t>9919991</t>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3372,7 +3363,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -3412,7 +3403,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>856</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3441,7 +3432,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3456,7 +3447,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3486,7 +3477,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>922</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3531,7 +3522,7 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>231</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -3555,12 +3546,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3575,7 +3566,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>184</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3585,7 +3576,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>02</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3605,17 +3596,17 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>296</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3630,7 +3621,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>293</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -3724,7 +3715,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -3734,12 +3725,12 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>182</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -3769,7 +3760,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>01</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
@@ -3823,7 +3814,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -3863,12 +3854,12 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -3878,12 +3869,12 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>000</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
@@ -3903,7 +3894,7 @@
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>122</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
@@ -3913,12 +3904,12 @@
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>278</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -4018,7 +4009,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>145</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -4053,7 +4044,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4082,7 +4073,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4117,13 +4108,13 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>921</t>
         </is>
       </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>451</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4138,7 +4129,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -4148,17 +4139,17 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
@@ -4207,7 +4198,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -4233,7 +4224,7 @@
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4243,7 +4234,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4321,12 +4312,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4346,7 +4337,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
@@ -4356,7 +4347,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -4372,12 +4363,12 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>876</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>912</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4412,7 +4403,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
@@ -4461,7 +4452,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -4502,7 +4493,7 @@
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>903</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4517,7 +4508,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -4527,12 +4518,12 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>482</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>262</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
@@ -4547,7 +4538,7 @@
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>803</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -4575,7 +4566,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -4630,7 +4621,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4665,7 +4656,7 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>238</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
@@ -4708,7 +4699,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4723,7 +4714,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -4758,12 +4749,12 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>286</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -4793,12 +4784,12 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>254</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
@@ -4823,7 +4814,7 @@
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>532</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -4842,7 +4833,7 @@
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -4857,7 +4848,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>156</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -4887,12 +4878,12 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>86</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -4922,7 +4913,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>442</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
@@ -5016,22 +5007,22 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>08</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -5041,12 +5032,12 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -5061,7 +5052,7 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
@@ -5081,7 +5072,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5100,7 +5091,7 @@
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>223</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -5110,7 +5101,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5135,12 +5126,12 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -5150,7 +5141,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>186</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -5180,7 +5171,7 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>492</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -5205,7 +5196,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>76</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -5274,13 +5265,13 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>966</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5300,7 +5291,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>251</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -5320,7 +5311,7 @@
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>241 7</t>
+          <t>241 0</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
@@ -5330,7 +5321,7 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
@@ -5353,7 +5344,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5403,12 +5394,12 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>182</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>298</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5423,7 +5414,7 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>312</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
@@ -5443,7 +5434,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>196</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
@@ -5453,12 +5444,12 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>258</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>216</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -5468,7 +5459,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>269</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -5502,7 +5493,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -5583,7 +5574,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -5628,7 +5619,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -5658,52 +5649,52 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
           <t>01</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X42" s="3" t="n"/>
@@ -5812,7 +5803,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>346</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -5847,12 +5838,12 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>146</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N45" s="3" t="n"/>
@@ -5868,7 +5859,7 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -5878,7 +5869,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -5888,7 +5879,7 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>963</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -5903,7 +5894,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -5913,7 +5904,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>822</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -5932,7 +5923,7 @@
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -5967,12 +5958,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>99</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>124</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -5982,42 +5973,42 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>223</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>298</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
@@ -6035,10 +6026,14 @@
           <t>602</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="n"/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>2 1</t>
+        </is>
+      </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>0 22</t>
+          <t>00 2989</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/508/508_198802_SF.JPG_stage_digit_manipulation.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>914</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>208</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>231</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>70</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>198</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>104</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>108</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>00</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1637,7 +1637,7 @@
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J11" s="3" t="n"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>905</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>67</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>192</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>74</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>0 1 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>08</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>919</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>207</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>875</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>143</t>
         </is>
       </c>
       <c r="K16" s="3" t="n"/>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>353</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>109</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>114</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>175</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>02</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>18</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2680,22 +2680,22 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>193</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>85</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>928</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>878</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>0 01</t>
+          <t>0 0</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>853</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -2897,12 +2897,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>288</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>00</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>88</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>178</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>139</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -3164,7 +3164,7 @@
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P23" s="3" t="n"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>360</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>577</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>812</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>788</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>673</t>
         </is>
       </c>
       <c r="Z25" s="3" t="n"/>
@@ -3546,67 +3546,67 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>918</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
@@ -3621,17 +3621,17 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>08</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>76</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>988</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>63</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>000</t>
+          <t>200</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>200</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -3984,7 +3984,7 @@
       <c r="M29" s="3" t="n"/>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>118</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4108,13 +4108,13 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>457</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4149,17 +4149,17 @@
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>104</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -4224,7 +4224,7 @@
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>280</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>263</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>258</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>146</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -4493,7 +4493,7 @@
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>803</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>278</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>78</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>242</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>290</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>09</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>876</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>274</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -4754,17 +4754,17 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>257</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -4878,17 +4878,17 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>155</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>928</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5007,17 +5007,17 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>99</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5126,37 +5126,37 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>000</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>00</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>886</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -5271,7 +5271,7 @@
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>95</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -5394,17 +5394,17 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>194</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>869</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>598</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>828</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>148</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" s="3" t="n"/>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -5838,18 +5838,18 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>311</t>
         </is>
       </c>
       <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>1069</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>241</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
@@ -5879,22 +5879,22 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
           <t>963</t>
         </is>
       </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>327</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -5948,42 +5948,42 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>92</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>97</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
@@ -6026,14 +6026,10 @@
           <t>602</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>2 1</t>
-        </is>
-      </c>
+      <c r="Y46" s="3" t="n"/>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>00 2989</t>
+          <t>0 2989</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
